--- a/fixtures/synthetic-capital/Fund II - Synthetic Value Fund II/Oakwood_Commons/acquisition/UW_OakwoodCommons_v3_AD_112020_FORMULA.xlsx
+++ b/fixtures/synthetic-capital/Fund II - Synthetic Value Fund II/Oakwood_Commons/acquisition/UW_OakwoodCommons_v3_AD_112020_FORMULA.xlsx
@@ -560,7 +560,7 @@
         <v>decimal</v>
       </c>
       <c r="D14" t="str">
-        <v>3.5% - Axiometrics shows 3.8%</v>
+        <v>3.5% - Synthetic Rent Survey shows 3.8%</v>
       </c>
     </row>
     <row r="15">
